--- a/01_Business_Understanding/RACI.xlsx
+++ b/01_Business_Understanding/RACI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta-my.sharepoint.com/personal/umgz4a_psoplaneta_com/Documents/DATA/Analytics Projects/Product_Analytics/01_Business_Understanding/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="8_{6380AE2C-335F-484B-8E5F-8DDF818B722F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08F9E1B1-F4B4-423E-9C07-F094A1214411}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="8_{6380AE2C-335F-484B-8E5F-8DDF818B722F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C37A7AE-87D2-4E0B-BEDD-8E44421EA82D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{35B2263B-5B1C-4573-BCAF-F7D0975E0BB0}"/>
   </bookViews>
@@ -488,10 +488,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1150,7 +1146,7 @@
       </c>
       <c r="F16" s="21"/>
       <c r="G16" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>9</v>
